--- a/output/2025-08-17.xlsx
+++ b/output/2025-08-17.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="F14" t="n">
-        <v>9.949999999999999</v>
+        <v>10.98</v>
       </c>
       <c r="G14" t="n">
-        <v>276.2</v>
+        <v>286.6</v>
       </c>
       <c r="H14" t="n">
-        <v>49.6</v>
+        <v>43.8</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>18.7</v>
+        <v>-29.61</v>
       </c>
       <c r="K14" t="n">
-        <v>33.17</v>
+        <v>110.57</v>
       </c>
       <c r="L14" t="n">
-        <v>38.08</v>
+        <v>114.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:51:53</t>
+          <t>05:52:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.81</v>
+        <v>2.91</v>
       </c>
       <c r="F15" t="n">
-        <v>10.74</v>
+        <v>9.99</v>
       </c>
       <c r="G15" t="n">
-        <v>296.7</v>
+        <v>289.2</v>
       </c>
       <c r="H15" t="n">
-        <v>50.7</v>
+        <v>37.9</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>56.64</v>
+        <v>10.11</v>
       </c>
       <c r="K15" t="n">
-        <v>-48.67</v>
+        <v>-72.91</v>
       </c>
       <c r="L15" t="n">
-        <v>74.68000000000001</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:54:05</t>
+          <t>05:53:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.01</v>
+        <v>4.01</v>
       </c>
       <c r="F16" t="n">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
       <c r="G16" t="n">
-        <v>271.4</v>
+        <v>285.4</v>
       </c>
       <c r="H16" t="n">
-        <v>41.4</v>
+        <v>48.5</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>74.61</v>
+        <v>-127.77</v>
       </c>
       <c r="K16" t="n">
-        <v>151.19</v>
+        <v>168.16</v>
       </c>
       <c r="L16" t="n">
-        <v>168.6</v>
+        <v>211.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:58:54</t>
+          <t>05:57:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="F17" t="n">
-        <v>10.41</v>
+        <v>10.66</v>
       </c>
       <c r="G17" t="n">
-        <v>295.9</v>
+        <v>296.2</v>
       </c>
       <c r="H17" t="n">
         <v>47.6</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>133.82</v>
+        <v>111.36</v>
       </c>
       <c r="K17" t="n">
-        <v>55.26</v>
+        <v>30.8</v>
       </c>
       <c r="L17" t="n">
-        <v>144.78</v>
+        <v>115.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:01:05</t>
+          <t>06:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="F18" t="n">
-        <v>9.73</v>
+        <v>10.58</v>
       </c>
       <c r="G18" t="n">
-        <v>272.2</v>
+        <v>258.2</v>
       </c>
       <c r="H18" t="n">
-        <v>47.7</v>
+        <v>40.5</v>
       </c>
       <c r="I18" t="n">
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>179.9</v>
+        <v>39.68</v>
       </c>
       <c r="K18" t="n">
-        <v>-30.65</v>
+        <v>158.51</v>
       </c>
       <c r="L18" t="n">
-        <v>182.49</v>
+        <v>163.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:02:28</t>
+          <t>06:01:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="F19" t="n">
-        <v>10.39</v>
+        <v>10.4</v>
       </c>
       <c r="G19" t="n">
-        <v>280.5</v>
+        <v>284.4</v>
       </c>
       <c r="H19" t="n">
-        <v>48.7</v>
+        <v>45.2</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>80.2</v>
+        <v>-51.8</v>
       </c>
       <c r="K19" t="n">
-        <v>228.43</v>
+        <v>-67.84</v>
       </c>
       <c r="L19" t="n">
-        <v>242.1</v>
+        <v>85.34999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:07:58</t>
+          <t>06:07:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="F20" t="n">
-        <v>10.88</v>
+        <v>10.38</v>
       </c>
       <c r="G20" t="n">
-        <v>289.1</v>
+        <v>284.2</v>
       </c>
       <c r="H20" t="n">
-        <v>45.6</v>
+        <v>55.4</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>34.35</v>
+        <v>427.24</v>
       </c>
       <c r="K20" t="n">
-        <v>201.16</v>
+        <v>-144.46</v>
       </c>
       <c r="L20" t="n">
-        <v>204.07</v>
+        <v>451</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:10:07</t>
+          <t>06:09:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="F21" t="n">
-        <v>10.34</v>
+        <v>10.75</v>
       </c>
       <c r="G21" t="n">
-        <v>275.2</v>
+        <v>274.2</v>
       </c>
       <c r="H21" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.86</v>
+        <v>-30.6</v>
       </c>
       <c r="K21" t="n">
-        <v>-508.63</v>
+        <v>-278.27</v>
       </c>
       <c r="L21" t="n">
-        <v>508.69</v>
+        <v>279.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:11:44</t>
+          <t>06:10:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="F22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.72</v>
       </c>
       <c r="G22" t="n">
-        <v>296.4</v>
+        <v>277.9</v>
       </c>
       <c r="H22" t="n">
-        <v>55.4</v>
+        <v>43.3</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>-71.36</v>
+        <v>12.06</v>
       </c>
       <c r="K22" t="n">
-        <v>-122.61</v>
+        <v>111.55</v>
       </c>
       <c r="L22" t="n">
-        <v>141.86</v>
+        <v>112.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:15:24</t>
+          <t>06:16:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="F23" t="n">
-        <v>10.37</v>
+        <v>10.5</v>
       </c>
       <c r="G23" t="n">
-        <v>292</v>
+        <v>292.8</v>
       </c>
       <c r="H23" t="n">
-        <v>43.8</v>
+        <v>49.9</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>82.89</v>
+        <v>-19.3</v>
       </c>
       <c r="K23" t="n">
-        <v>-358.22</v>
+        <v>-336.93</v>
       </c>
       <c r="L23" t="n">
-        <v>367.69</v>
+        <v>337.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:17:26</t>
+          <t>06:18:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="F24" t="n">
-        <v>10.46</v>
+        <v>10.58</v>
       </c>
       <c r="G24" t="n">
-        <v>291</v>
+        <v>280.2</v>
       </c>
       <c r="H24" t="n">
-        <v>46.3</v>
+        <v>44.8</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>354.57</v>
+        <v>-366.07</v>
       </c>
       <c r="K24" t="n">
-        <v>-88.29000000000001</v>
+        <v>181.08</v>
       </c>
       <c r="L24" t="n">
-        <v>365.4</v>
+        <v>408.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:19:15</t>
+          <t>06:20:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="F25" t="n">
-        <v>9.85</v>
+        <v>10.09</v>
       </c>
       <c r="G25" t="n">
-        <v>288.8</v>
+        <v>302.7</v>
       </c>
       <c r="H25" t="n">
-        <v>46.6</v>
+        <v>41.4</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-173.09</v>
+        <v>-0.28</v>
       </c>
       <c r="K25" t="n">
-        <v>244.06</v>
+        <v>298.95</v>
       </c>
       <c r="L25" t="n">
-        <v>299.21</v>
+        <v>298.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:24:17</t>
+          <t>06:23:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="F26" t="n">
-        <v>9.6</v>
+        <v>10.69</v>
       </c>
       <c r="G26" t="n">
-        <v>283.9</v>
+        <v>286.3</v>
       </c>
       <c r="H26" t="n">
-        <v>48.3</v>
+        <v>47.7</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>-292.83</v>
+        <v>42.55</v>
       </c>
       <c r="K26" t="n">
-        <v>424.5</v>
+        <v>372.15</v>
       </c>
       <c r="L26" t="n">
-        <v>515.7</v>
+        <v>374.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:26:32</t>
+          <t>06:25:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="F27" t="n">
         <v>10.35</v>
       </c>
       <c r="G27" t="n">
-        <v>280.8</v>
+        <v>284.3</v>
       </c>
       <c r="H27" t="n">
-        <v>47</v>
+        <v>47.9</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>310.85</v>
+        <v>783.0700000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-141.87</v>
+        <v>417.73</v>
       </c>
       <c r="L27" t="n">
-        <v>341.69</v>
+        <v>887.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:27:20</t>
+          <t>06:26:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.82</v>
+        <v>3.36</v>
       </c>
       <c r="F28" t="n">
-        <v>10.18</v>
+        <v>10.35</v>
       </c>
       <c r="G28" t="n">
-        <v>298.2</v>
+        <v>284.6</v>
       </c>
       <c r="H28" t="n">
-        <v>56.1</v>
+        <v>44.3</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-403.43</v>
+        <v>114.07</v>
       </c>
       <c r="K28" t="n">
-        <v>-685.1799999999999</v>
+        <v>400.75</v>
       </c>
       <c r="L28" t="n">
-        <v>795.13</v>
+        <v>416.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:40:21</t>
+          <t>06:39:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.86</v>
+        <v>2.31</v>
       </c>
       <c r="F29" t="n">
-        <v>9.9</v>
+        <v>10.59</v>
       </c>
       <c r="G29" t="n">
-        <v>285.3</v>
+        <v>279.4</v>
       </c>
       <c r="H29" t="n">
-        <v>50.7</v>
+        <v>49.6</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>137.89</v>
+        <v>-23.84</v>
       </c>
       <c r="K29" t="n">
-        <v>166.22</v>
+        <v>-107.06</v>
       </c>
       <c r="L29" t="n">
-        <v>215.96</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:42:02</t>
+          <t>06:42:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="F30" t="n">
-        <v>10.63</v>
+        <v>10.28</v>
       </c>
       <c r="G30" t="n">
-        <v>294.6</v>
+        <v>291.5</v>
       </c>
       <c r="H30" t="n">
-        <v>44.5</v>
+        <v>46.2</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-27.14</v>
+        <v>-54.15</v>
       </c>
       <c r="K30" t="n">
-        <v>-59.12</v>
+        <v>174.89</v>
       </c>
       <c r="L30" t="n">
-        <v>65.05</v>
+        <v>183.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:43:05</t>
+          <t>06:42:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="F31" t="n">
-        <v>10.21</v>
+        <v>10.4</v>
       </c>
       <c r="G31" t="n">
-        <v>279.8</v>
+        <v>282.1</v>
       </c>
       <c r="H31" t="n">
-        <v>48.5</v>
+        <v>46.2</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>67.91</v>
+        <v>-79.7</v>
       </c>
       <c r="K31" t="n">
-        <v>80.91</v>
+        <v>-118.8</v>
       </c>
       <c r="L31" t="n">
-        <v>105.63</v>
+        <v>143.05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:47:01</t>
+          <t>06:47:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="F32" t="n">
-        <v>10.41</v>
+        <v>9.98</v>
       </c>
       <c r="G32" t="n">
-        <v>292.7</v>
+        <v>283.6</v>
       </c>
       <c r="H32" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-139.73</v>
+        <v>34.25</v>
       </c>
       <c r="K32" t="n">
-        <v>152.71</v>
+        <v>207.64</v>
       </c>
       <c r="L32" t="n">
-        <v>206.99</v>
+        <v>210.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:48:13</t>
+          <t>06:48:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="F33" t="n">
-        <v>9.84</v>
+        <v>11.07</v>
       </c>
       <c r="G33" t="n">
-        <v>290</v>
+        <v>294.3</v>
       </c>
       <c r="H33" t="n">
-        <v>46</v>
+        <v>49.1</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>36.41</v>
+        <v>76.59</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.52</v>
+        <v>-32.34</v>
       </c>
       <c r="L33" t="n">
-        <v>36.49</v>
+        <v>83.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:50:15</t>
+          <t>06:50:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="F34" t="n">
-        <v>10.85</v>
+        <v>10.55</v>
       </c>
       <c r="G34" t="n">
-        <v>272.2</v>
+        <v>287.3</v>
       </c>
       <c r="H34" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>145.7</v>
+        <v>-55.27</v>
       </c>
       <c r="K34" t="n">
-        <v>115.87</v>
+        <v>23.97</v>
       </c>
       <c r="L34" t="n">
-        <v>186.15</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:54:11</t>
+          <t>06:56:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.41</v>
+        <v>2.78</v>
       </c>
       <c r="F35" t="n">
-        <v>10.26</v>
+        <v>10.5</v>
       </c>
       <c r="G35" t="n">
-        <v>283.8</v>
+        <v>290</v>
       </c>
       <c r="H35" t="n">
-        <v>47.4</v>
+        <v>43.5</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-65.06</v>
+        <v>117.46</v>
       </c>
       <c r="K35" t="n">
-        <v>-4</v>
+        <v>138.05</v>
       </c>
       <c r="L35" t="n">
-        <v>65.18000000000001</v>
+        <v>181.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:55:11</t>
+          <t>06:56:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="F36" t="n">
-        <v>10.72</v>
+        <v>10.5</v>
       </c>
       <c r="G36" t="n">
-        <v>294.4</v>
+        <v>281.4</v>
       </c>
       <c r="H36" t="n">
-        <v>48.8</v>
+        <v>47.9</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>361.33</v>
+        <v>233.01</v>
       </c>
       <c r="K36" t="n">
-        <v>104.71</v>
+        <v>-107.93</v>
       </c>
       <c r="L36" t="n">
-        <v>376.2</v>
+        <v>256.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:57:33</t>
+          <t>06:58:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.19</v>
+        <v>3.26</v>
       </c>
       <c r="F37" t="n">
-        <v>10.37</v>
+        <v>10.24</v>
       </c>
       <c r="G37" t="n">
-        <v>290</v>
+        <v>272.3</v>
       </c>
       <c r="H37" t="n">
-        <v>44.7</v>
+        <v>50.6</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-99.18000000000001</v>
+        <v>-47.79</v>
       </c>
       <c r="K37" t="n">
-        <v>-185.89</v>
+        <v>27.27</v>
       </c>
       <c r="L37" t="n">
-        <v>210.69</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:01:54</t>
+          <t>07:04:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.86</v>
+        <v>3.14</v>
       </c>
       <c r="F38" t="n">
-        <v>10.48</v>
+        <v>10.16</v>
       </c>
       <c r="G38" t="n">
-        <v>299.7</v>
+        <v>307.2</v>
       </c>
       <c r="H38" t="n">
-        <v>44.5</v>
+        <v>47.7</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-110.29</v>
+        <v>-365.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-174.15</v>
+        <v>177.41</v>
       </c>
       <c r="L38" t="n">
-        <v>206.14</v>
+        <v>406.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:03:15</t>
+          <t>07:05:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.96</v>
+        <v>2.6</v>
       </c>
       <c r="F39" t="n">
-        <v>9.52</v>
+        <v>9.92</v>
       </c>
       <c r="G39" t="n">
-        <v>284.3</v>
+        <v>296.9</v>
       </c>
       <c r="H39" t="n">
-        <v>47.6</v>
+        <v>49.9</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>169.64</v>
+        <v>-554.39</v>
       </c>
       <c r="K39" t="n">
-        <v>435.32</v>
+        <v>-142.81</v>
       </c>
       <c r="L39" t="n">
-        <v>467.2</v>
+        <v>572.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:05:50</t>
+          <t>07:07:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.45</v>
+        <v>3.33</v>
       </c>
       <c r="F40" t="n">
-        <v>9.720000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="G40" t="n">
-        <v>294.8</v>
+        <v>268.4</v>
       </c>
       <c r="H40" t="n">
-        <v>58.1</v>
+        <v>52.1</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>508.56</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>245.32</v>
+        <v>156.33</v>
       </c>
       <c r="L40" t="n">
-        <v>564.63</v>
+        <v>183.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:10:52</t>
+          <t>07:12:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.64</v>
+        <v>3.22</v>
       </c>
       <c r="F41" t="n">
-        <v>9.99</v>
+        <v>9.73</v>
       </c>
       <c r="G41" t="n">
-        <v>288.8</v>
+        <v>276.2</v>
       </c>
       <c r="H41" t="n">
-        <v>47</v>
+        <v>57.4</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>234.11</v>
+        <v>-452.5</v>
       </c>
       <c r="K41" t="n">
-        <v>98.81</v>
+        <v>672.8099999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>254.11</v>
+        <v>810.8200000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:12:36</t>
+          <t>07:13:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.92</v>
+        <v>4.05</v>
       </c>
       <c r="F42" t="n">
-        <v>10.2</v>
+        <v>10.71</v>
       </c>
       <c r="G42" t="n">
-        <v>286.3</v>
+        <v>271.7</v>
       </c>
       <c r="H42" t="n">
-        <v>52.4</v>
+        <v>49.3</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>472.72</v>
+        <v>-675.7</v>
       </c>
       <c r="K42" t="n">
-        <v>612.98</v>
+        <v>54.67</v>
       </c>
       <c r="L42" t="n">
-        <v>774.09</v>
+        <v>677.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:14:06</t>
+          <t>07:14:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="F43" t="n">
-        <v>11.23</v>
+        <v>9.98</v>
       </c>
       <c r="G43" t="n">
-        <v>290.7</v>
+        <v>283.8</v>
       </c>
       <c r="H43" t="n">
-        <v>51.4</v>
+        <v>41.5</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-81.31999999999999</v>
+        <v>228.73</v>
       </c>
       <c r="K43" t="n">
-        <v>-676.64</v>
+        <v>149.28</v>
       </c>
       <c r="L43" t="n">
-        <v>681.51</v>
+        <v>273.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:24:29</t>
+          <t>07:26:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="F44" t="n">
-        <v>10.21</v>
+        <v>10.53</v>
       </c>
       <c r="G44" t="n">
-        <v>283.4</v>
+        <v>282.4</v>
       </c>
       <c r="H44" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-21.76</v>
+        <v>-58.2</v>
       </c>
       <c r="K44" t="n">
-        <v>-55.05</v>
+        <v>174.2</v>
       </c>
       <c r="L44" t="n">
-        <v>59.2</v>
+        <v>183.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:26:16</t>
+          <t>07:27:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.15</v>
+        <v>3.51</v>
       </c>
       <c r="F45" t="n">
-        <v>10.35</v>
+        <v>10.18</v>
       </c>
       <c r="G45" t="n">
-        <v>303.3</v>
+        <v>276.1</v>
       </c>
       <c r="H45" t="n">
-        <v>44.3</v>
+        <v>51.6</v>
       </c>
       <c r="I45" t="n">
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-61.89</v>
+        <v>-4.26</v>
       </c>
       <c r="K45" t="n">
-        <v>33.16</v>
+        <v>114.03</v>
       </c>
       <c r="L45" t="n">
-        <v>70.20999999999999</v>
+        <v>114.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:28:14</t>
+          <t>07:28:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="F46" t="n">
-        <v>10.08</v>
+        <v>10.78</v>
       </c>
       <c r="G46" t="n">
-        <v>292.8</v>
+        <v>285</v>
       </c>
       <c r="H46" t="n">
-        <v>37.2</v>
+        <v>48.6</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>151.45</v>
+        <v>107.88</v>
       </c>
       <c r="K46" t="n">
-        <v>94.98999999999999</v>
+        <v>-205.49</v>
       </c>
       <c r="L46" t="n">
-        <v>178.77</v>
+        <v>232.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:33:01</t>
+          <t>07:32:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.75</v>
+        <v>2.99</v>
       </c>
       <c r="F47" t="n">
-        <v>10.24</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>273.7</v>
+        <v>284.2</v>
       </c>
       <c r="H47" t="n">
-        <v>41.8</v>
+        <v>46.7</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>185.36</v>
+        <v>83.2</v>
       </c>
       <c r="K47" t="n">
-        <v>1.84</v>
+        <v>196.48</v>
       </c>
       <c r="L47" t="n">
-        <v>185.37</v>
+        <v>213.37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:35:03</t>
+          <t>07:34:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.77</v>
+        <v>3.12</v>
       </c>
       <c r="F48" t="n">
-        <v>10.35</v>
+        <v>10.79</v>
       </c>
       <c r="G48" t="n">
-        <v>281.3</v>
+        <v>273.4</v>
       </c>
       <c r="H48" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>107.58</v>
+        <v>46.45</v>
       </c>
       <c r="K48" t="n">
-        <v>44.11</v>
+        <v>50.8</v>
       </c>
       <c r="L48" t="n">
-        <v>116.27</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:37:19</t>
+          <t>07:36:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.93</v>
+        <v>4.09</v>
       </c>
       <c r="F49" t="n">
-        <v>10.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>276.1</v>
+        <v>300.7</v>
       </c>
       <c r="H49" t="n">
-        <v>53.3</v>
+        <v>51.4</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-203.15</v>
+        <v>-271.38</v>
       </c>
       <c r="K49" t="n">
-        <v>84.14</v>
+        <v>-305.07</v>
       </c>
       <c r="L49" t="n">
-        <v>219.88</v>
+        <v>408.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:43:15</t>
+          <t>07:39:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>10.55</v>
       </c>
       <c r="G50" t="n">
-        <v>266.5</v>
+        <v>293.1</v>
       </c>
       <c r="H50" t="n">
-        <v>45.6</v>
+        <v>46.4</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>283.43</v>
+        <v>-102.22</v>
       </c>
       <c r="K50" t="n">
-        <v>-87.3</v>
+        <v>347.14</v>
       </c>
       <c r="L50" t="n">
-        <v>296.57</v>
+        <v>361.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:44:25</t>
+          <t>07:41:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="F51" t="n">
-        <v>10.65</v>
+        <v>10.22</v>
       </c>
       <c r="G51" t="n">
-        <v>275.1</v>
+        <v>302.3</v>
       </c>
       <c r="H51" t="n">
-        <v>52.6</v>
+        <v>46.9</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-118.88</v>
+        <v>-339.65</v>
       </c>
       <c r="K51" t="n">
-        <v>-147.25</v>
+        <v>-116.74</v>
       </c>
       <c r="L51" t="n">
-        <v>189.25</v>
+        <v>359.15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:46:13</t>
+          <t>07:43:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.37</v>
+        <v>3.06</v>
       </c>
       <c r="F52" t="n">
-        <v>10.27</v>
+        <v>10.06</v>
       </c>
       <c r="G52" t="n">
-        <v>288.7</v>
+        <v>286.7</v>
       </c>
       <c r="H52" t="n">
-        <v>49.3</v>
+        <v>45</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-92.23999999999999</v>
+        <v>-236.22</v>
       </c>
       <c r="K52" t="n">
-        <v>168.47</v>
+        <v>-29.54</v>
       </c>
       <c r="L52" t="n">
-        <v>192.07</v>
+        <v>238.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:51:38</t>
+          <t>07:49:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="F53" t="n">
-        <v>10.05</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>283.5</v>
+        <v>283.7</v>
       </c>
       <c r="H53" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>47.31</v>
+        <v>426.31</v>
       </c>
       <c r="K53" t="n">
-        <v>109.06</v>
+        <v>-30.43</v>
       </c>
       <c r="L53" t="n">
-        <v>118.88</v>
+        <v>427.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:53:31</t>
+          <t>07:50:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="F54" t="n">
-        <v>10.36</v>
+        <v>10.28</v>
       </c>
       <c r="G54" t="n">
-        <v>279.6</v>
+        <v>297.8</v>
       </c>
       <c r="H54" t="n">
-        <v>50.8</v>
+        <v>53.1</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>63.35</v>
+        <v>-242.56</v>
       </c>
       <c r="K54" t="n">
-        <v>-337.17</v>
+        <v>293.17</v>
       </c>
       <c r="L54" t="n">
-        <v>343.07</v>
+        <v>380.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:54:55</t>
+          <t>07:51:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="F55" t="n">
-        <v>10.16</v>
+        <v>10.02</v>
       </c>
       <c r="G55" t="n">
-        <v>276.8</v>
+        <v>279.1</v>
       </c>
       <c r="H55" t="n">
-        <v>51.1</v>
+        <v>48</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-296.82</v>
+        <v>86.72</v>
       </c>
       <c r="K55" t="n">
-        <v>-234.55</v>
+        <v>-242.5</v>
       </c>
       <c r="L55" t="n">
-        <v>378.3</v>
+        <v>257.54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:59:13</t>
+          <t>07:57:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.93</v>
+        <v>3.71</v>
       </c>
       <c r="F56" t="n">
-        <v>10.18</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>275.3</v>
+        <v>282.7</v>
       </c>
       <c r="H56" t="n">
-        <v>45.9</v>
+        <v>50.3</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>498.84</v>
+        <v>24.4</v>
       </c>
       <c r="K56" t="n">
-        <v>245.76</v>
+        <v>85.05</v>
       </c>
       <c r="L56" t="n">
-        <v>556.1</v>
+        <v>88.48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:00:11</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="F57" t="n">
-        <v>10.05</v>
+        <v>10.55</v>
       </c>
       <c r="G57" t="n">
-        <v>273.4</v>
+        <v>287.3</v>
       </c>
       <c r="H57" t="n">
-        <v>46.1</v>
+        <v>36.3</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-225.06</v>
+        <v>207.86</v>
       </c>
       <c r="K57" t="n">
-        <v>-262.98</v>
+        <v>-398.21</v>
       </c>
       <c r="L57" t="n">
-        <v>346.13</v>
+        <v>449.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:01:33</t>
+          <t>08:00:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.86</v>
+        <v>3.18</v>
       </c>
       <c r="F58" t="n">
-        <v>10.65</v>
+        <v>11.12</v>
       </c>
       <c r="G58" t="n">
-        <v>293.1</v>
+        <v>279</v>
       </c>
       <c r="H58" t="n">
-        <v>48.5</v>
+        <v>50.9</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>408.96</v>
+        <v>242.4</v>
       </c>
       <c r="K58" t="n">
-        <v>-481.86</v>
+        <v>-175.02</v>
       </c>
       <c r="L58" t="n">
-        <v>632.01</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:11:36</t>
+          <t>08:12:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.22</v>
+        <v>3.76</v>
       </c>
       <c r="F59" t="n">
-        <v>10.48</v>
+        <v>10.42</v>
       </c>
       <c r="G59" t="n">
-        <v>273.1</v>
+        <v>296.5</v>
       </c>
       <c r="H59" t="n">
-        <v>44.7</v>
+        <v>49.2</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-32.57</v>
+        <v>6.85</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.96</v>
+        <v>-111.5</v>
       </c>
       <c r="L59" t="n">
-        <v>55.52</v>
+        <v>111.71</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:13:37</t>
+          <t>08:14:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.73</v>
+        <v>3.38</v>
       </c>
       <c r="F60" t="n">
-        <v>10.55</v>
+        <v>9.85</v>
       </c>
       <c r="G60" t="n">
-        <v>280.5</v>
+        <v>272</v>
       </c>
       <c r="H60" t="n">
-        <v>51.6</v>
+        <v>49.6</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>35.41</v>
+        <v>-21.98</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.04</v>
+        <v>-179.36</v>
       </c>
       <c r="L60" t="n">
-        <v>41.19</v>
+        <v>180.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:14:41</t>
+          <t>08:16:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="F61" t="n">
-        <v>9.960000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="G61" t="n">
-        <v>288.7</v>
+        <v>281.6</v>
       </c>
       <c r="H61" t="n">
-        <v>49.5</v>
+        <v>38</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>38.31</v>
+        <v>51.32</v>
       </c>
       <c r="K61" t="n">
-        <v>-94.8</v>
+        <v>75.72</v>
       </c>
       <c r="L61" t="n">
-        <v>102.25</v>
+        <v>91.47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:20:15</t>
+          <t>08:20:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.97</v>
+        <v>3.03</v>
       </c>
       <c r="F62" t="n">
-        <v>10.76</v>
+        <v>10.14</v>
       </c>
       <c r="G62" t="n">
-        <v>283</v>
+        <v>287.2</v>
       </c>
       <c r="H62" t="n">
-        <v>48.2</v>
+        <v>50</v>
       </c>
       <c r="I62" t="n">
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-24.07</v>
+        <v>-167.53</v>
       </c>
       <c r="K62" t="n">
-        <v>-20.83</v>
+        <v>89.08</v>
       </c>
       <c r="L62" t="n">
-        <v>31.83</v>
+        <v>189.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:21:15</t>
+          <t>08:21:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="F63" t="n">
-        <v>10.31</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>292.2</v>
+        <v>282.4</v>
       </c>
       <c r="H63" t="n">
-        <v>54</v>
+        <v>49.3</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-52.83</v>
+        <v>-114.14</v>
       </c>
       <c r="K63" t="n">
-        <v>54.95</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>76.23</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:22:48</t>
+          <t>08:23:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.52</v>
+        <v>3.18</v>
       </c>
       <c r="F64" t="n">
-        <v>9.94</v>
+        <v>10.34</v>
       </c>
       <c r="G64" t="n">
-        <v>291.8</v>
+        <v>282.9</v>
       </c>
       <c r="H64" t="n">
-        <v>44.3</v>
+        <v>42.6</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>345.98</v>
+        <v>-117.16</v>
       </c>
       <c r="K64" t="n">
-        <v>-25.16</v>
+        <v>117.83</v>
       </c>
       <c r="L64" t="n">
-        <v>346.89</v>
+        <v>166.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:27:36</t>
+          <t>08:27:38</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.8</v>
+        <v>3.73</v>
       </c>
       <c r="F65" t="n">
-        <v>10.35</v>
+        <v>10.17</v>
       </c>
       <c r="G65" t="n">
-        <v>293</v>
+        <v>290.6</v>
       </c>
       <c r="H65" t="n">
-        <v>50.3</v>
+        <v>45.6</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>4.2</v>
+        <v>196.15</v>
       </c>
       <c r="K65" t="n">
-        <v>-101.57</v>
+        <v>97.86</v>
       </c>
       <c r="L65" t="n">
-        <v>101.65</v>
+        <v>219.21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:28:21</t>
+          <t>08:29:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="F66" t="n">
-        <v>10.2</v>
+        <v>10.27</v>
       </c>
       <c r="G66" t="n">
-        <v>280.2</v>
+        <v>285.9</v>
       </c>
       <c r="H66" t="n">
-        <v>53.3</v>
+        <v>41.5</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.06</v>
+        <v>417.54</v>
       </c>
       <c r="K66" t="n">
-        <v>-103.13</v>
+        <v>105.43</v>
       </c>
       <c r="L66" t="n">
-        <v>104.7</v>
+        <v>430.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:30:41</t>
+          <t>08:30:05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="F67" t="n">
-        <v>10.69</v>
+        <v>10.12</v>
       </c>
       <c r="G67" t="n">
-        <v>286.8</v>
+        <v>287</v>
       </c>
       <c r="H67" t="n">
-        <v>48.6</v>
+        <v>51.4</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-93.81999999999999</v>
+        <v>-95.39</v>
       </c>
       <c r="K67" t="n">
-        <v>-136.3</v>
+        <v>310.26</v>
       </c>
       <c r="L67" t="n">
-        <v>165.47</v>
+        <v>324.59</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:35:06</t>
+          <t>08:34:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.07</v>
+        <v>3.67</v>
       </c>
       <c r="F68" t="n">
-        <v>9.76</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>289.5</v>
+        <v>288.7</v>
       </c>
       <c r="H68" t="n">
-        <v>45.7</v>
+        <v>39.9</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-484.92</v>
+        <v>-242.97</v>
       </c>
       <c r="K68" t="n">
-        <v>266.28</v>
+        <v>-163.24</v>
       </c>
       <c r="L68" t="n">
-        <v>553.22</v>
+        <v>292.71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:36:39</t>
+          <t>08:36:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="F69" t="n">
-        <v>10.03</v>
+        <v>10.27</v>
       </c>
       <c r="G69" t="n">
-        <v>288.3</v>
+        <v>289</v>
       </c>
       <c r="H69" t="n">
-        <v>43.3</v>
+        <v>51.1</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-546.53</v>
+        <v>113.94</v>
       </c>
       <c r="K69" t="n">
-        <v>-420.15</v>
+        <v>-121.93</v>
       </c>
       <c r="L69" t="n">
-        <v>689.36</v>
+        <v>166.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:37:21</t>
+          <t>08:38:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="F70" t="n">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="G70" t="n">
-        <v>286.7</v>
+        <v>274.2</v>
       </c>
       <c r="H70" t="n">
-        <v>48.5</v>
+        <v>55</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>603.59</v>
+        <v>-84.29000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-43.84</v>
+        <v>-376.49</v>
       </c>
       <c r="L70" t="n">
-        <v>605.1799999999999</v>
+        <v>385.81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:43:06</t>
+          <t>08:43:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="F71" t="n">
-        <v>10.9</v>
+        <v>10.52</v>
       </c>
       <c r="G71" t="n">
-        <v>291.1</v>
+        <v>278.2</v>
       </c>
       <c r="H71" t="n">
-        <v>46.6</v>
+        <v>52.2</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>182.01</v>
+        <v>-255.37</v>
       </c>
       <c r="K71" t="n">
-        <v>-388.96</v>
+        <v>-299.65</v>
       </c>
       <c r="L71" t="n">
-        <v>429.44</v>
+        <v>393.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:45:23</t>
+          <t>08:45:49</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="F72" t="n">
-        <v>9.550000000000001</v>
+        <v>10.31</v>
       </c>
       <c r="G72" t="n">
-        <v>288.8</v>
+        <v>291</v>
       </c>
       <c r="H72" t="n">
-        <v>45.9</v>
+        <v>46.8</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>244.56</v>
+        <v>121.62</v>
       </c>
       <c r="K72" t="n">
-        <v>137.35</v>
+        <v>-134.34</v>
       </c>
       <c r="L72" t="n">
-        <v>280.49</v>
+        <v>181.21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:47:19</t>
+          <t>08:47:47</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="F73" t="n">
-        <v>10.19</v>
+        <v>10.27</v>
       </c>
       <c r="G73" t="n">
-        <v>301.4</v>
+        <v>284.3</v>
       </c>
       <c r="H73" t="n">
-        <v>55</v>
+        <v>43.2</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-848.26</v>
+        <v>153.99</v>
       </c>
       <c r="K73" t="n">
-        <v>-474.48</v>
+        <v>-31.7</v>
       </c>
       <c r="L73" t="n">
-        <v>971.9400000000001</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:57:45</t>
+          <t>08:57:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3148,31 +3148,31 @@
         <v>3.3</v>
       </c>
       <c r="F74" t="n">
-        <v>10.04</v>
+        <v>10.82</v>
       </c>
       <c r="G74" t="n">
-        <v>296.5</v>
+        <v>269.1</v>
       </c>
       <c r="H74" t="n">
-        <v>48.8</v>
+        <v>52.9</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>46.33</v>
+        <v>-98.66</v>
       </c>
       <c r="K74" t="n">
-        <v>130.32</v>
+        <v>-49.44</v>
       </c>
       <c r="L74" t="n">
-        <v>138.31</v>
+        <v>110.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:00:35</t>
+          <t>09:00:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="F75" t="n">
-        <v>9.99</v>
+        <v>10.57</v>
       </c>
       <c r="G75" t="n">
-        <v>289.7</v>
+        <v>271</v>
       </c>
       <c r="H75" t="n">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>132.22</v>
+        <v>-174.04</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.9</v>
+        <v>20.85</v>
       </c>
       <c r="L75" t="n">
-        <v>143.55</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:01:13</t>
+          <t>09:02:43</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.02</v>
+        <v>3.66</v>
       </c>
       <c r="F76" t="n">
-        <v>10.8</v>
+        <v>10.52</v>
       </c>
       <c r="G76" t="n">
-        <v>296.4</v>
+        <v>280.9</v>
       </c>
       <c r="H76" t="n">
-        <v>39.6</v>
+        <v>49.2</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>-94.73</v>
+        <v>143.3</v>
       </c>
       <c r="K76" t="n">
-        <v>9.18</v>
+        <v>-33.64</v>
       </c>
       <c r="L76" t="n">
-        <v>95.17</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:06:38</t>
+          <t>09:07:17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="F77" t="n">
-        <v>9.789999999999999</v>
+        <v>10.39</v>
       </c>
       <c r="G77" t="n">
-        <v>291.3</v>
+        <v>294.8</v>
       </c>
       <c r="H77" t="n">
-        <v>48.4</v>
+        <v>45.2</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>115.91</v>
+        <v>-82.25</v>
       </c>
       <c r="K77" t="n">
-        <v>-100.56</v>
+        <v>-173.57</v>
       </c>
       <c r="L77" t="n">
-        <v>153.45</v>
+        <v>192.07</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:08:04</t>
+          <t>09:08:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="F78" t="n">
-        <v>9.880000000000001</v>
+        <v>10.52</v>
       </c>
       <c r="G78" t="n">
-        <v>294</v>
+        <v>286.4</v>
       </c>
       <c r="H78" t="n">
-        <v>46.7</v>
+        <v>42.4</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-35.77</v>
+        <v>151.05</v>
       </c>
       <c r="K78" t="n">
-        <v>106.82</v>
+        <v>347.6</v>
       </c>
       <c r="L78" t="n">
-        <v>112.64</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:09:39</t>
+          <t>09:09:50</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.52</v>
+        <v>3.47</v>
       </c>
       <c r="F79" t="n">
-        <v>10.52</v>
+        <v>11.04</v>
       </c>
       <c r="G79" t="n">
-        <v>289.1</v>
+        <v>279.2</v>
       </c>
       <c r="H79" t="n">
-        <v>42</v>
+        <v>55.6</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>26.03</v>
+        <v>-115.56</v>
       </c>
       <c r="K79" t="n">
-        <v>42.29</v>
+        <v>145.75</v>
       </c>
       <c r="L79" t="n">
-        <v>49.66</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:15:44</t>
+          <t>09:14:39</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="F80" t="n">
-        <v>10.26</v>
+        <v>10.44</v>
       </c>
       <c r="G80" t="n">
-        <v>286.8</v>
+        <v>288.4</v>
       </c>
       <c r="H80" t="n">
-        <v>40.5</v>
+        <v>47.6</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>86.42</v>
+        <v>103.52</v>
       </c>
       <c r="K80" t="n">
-        <v>-107.75</v>
+        <v>-157.83</v>
       </c>
       <c r="L80" t="n">
-        <v>138.13</v>
+        <v>188.75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:18:10</t>
+          <t>09:16:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.56</v>
+        <v>3.73</v>
       </c>
       <c r="F81" t="n">
-        <v>11.15</v>
+        <v>11.01</v>
       </c>
       <c r="G81" t="n">
-        <v>283.2</v>
+        <v>291.6</v>
       </c>
       <c r="H81" t="n">
-        <v>42.7</v>
+        <v>46.9</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-207.08</v>
+        <v>-111.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-32.24</v>
+        <v>-165.33</v>
       </c>
       <c r="L81" t="n">
-        <v>209.58</v>
+        <v>199.22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:20:16</t>
+          <t>09:17:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.01</v>
+        <v>3.76</v>
       </c>
       <c r="F82" t="n">
-        <v>10.64</v>
+        <v>10.77</v>
       </c>
       <c r="G82" t="n">
-        <v>264.8</v>
+        <v>293.9</v>
       </c>
       <c r="H82" t="n">
-        <v>51.9</v>
+        <v>46.1</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-86.67</v>
+        <v>-320.15</v>
       </c>
       <c r="K82" t="n">
-        <v>22.87</v>
+        <v>-12.21</v>
       </c>
       <c r="L82" t="n">
-        <v>89.63</v>
+        <v>320.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:25:12</t>
+          <t>09:22:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.69</v>
+        <v>3.12</v>
       </c>
       <c r="F83" t="n">
-        <v>9.9</v>
+        <v>11.28</v>
       </c>
       <c r="G83" t="n">
-        <v>286.3</v>
+        <v>291.5</v>
       </c>
       <c r="H83" t="n">
-        <v>50.3</v>
+        <v>52.3</v>
       </c>
       <c r="I83" t="n">
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>201.41</v>
+        <v>317.86</v>
       </c>
       <c r="K83" t="n">
-        <v>-21.45</v>
+        <v>139.29</v>
       </c>
       <c r="L83" t="n">
-        <v>202.55</v>
+        <v>347.04</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:26:55</t>
+          <t>09:23:58</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.73</v>
+        <v>3.31</v>
       </c>
       <c r="F84" t="n">
-        <v>9.890000000000001</v>
+        <v>10.69</v>
       </c>
       <c r="G84" t="n">
-        <v>288.2</v>
+        <v>288.4</v>
       </c>
       <c r="H84" t="n">
-        <v>48.9</v>
+        <v>45.9</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-174.97</v>
+        <v>192.3</v>
       </c>
       <c r="K84" t="n">
-        <v>-542.0700000000001</v>
+        <v>343.9</v>
       </c>
       <c r="L84" t="n">
-        <v>569.61</v>
+        <v>394.01</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:28:44</t>
+          <t>09:24:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.86</v>
+        <v>3.99</v>
       </c>
       <c r="F85" t="n">
-        <v>10.3</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>286</v>
+        <v>277.6</v>
       </c>
       <c r="H85" t="n">
-        <v>52.5</v>
+        <v>50.9</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-331.01</v>
+        <v>-212.85</v>
       </c>
       <c r="K85" t="n">
-        <v>-234.82</v>
+        <v>-58.21</v>
       </c>
       <c r="L85" t="n">
-        <v>405.85</v>
+        <v>220.67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:33:06</t>
+          <t>09:28:50</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3652,31 +3652,31 @@
         <v>3.35</v>
       </c>
       <c r="F86" t="n">
-        <v>10.45</v>
+        <v>10.51</v>
       </c>
       <c r="G86" t="n">
-        <v>291.4</v>
+        <v>291</v>
       </c>
       <c r="H86" t="n">
-        <v>49.4</v>
+        <v>46.3</v>
       </c>
       <c r="I86" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-333.72</v>
+        <v>490.94</v>
       </c>
       <c r="K86" t="n">
-        <v>-50.87</v>
+        <v>256.26</v>
       </c>
       <c r="L86" t="n">
-        <v>337.58</v>
+        <v>553.8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:35:05</t>
+          <t>09:30:18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.41</v>
+        <v>3.56</v>
       </c>
       <c r="F87" t="n">
-        <v>10.12</v>
+        <v>10.63</v>
       </c>
       <c r="G87" t="n">
-        <v>280.9</v>
+        <v>271.3</v>
       </c>
       <c r="H87" t="n">
-        <v>47.7</v>
+        <v>51.6</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-176.13</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-430.72</v>
+        <v>-326.16</v>
       </c>
       <c r="L87" t="n">
-        <v>465.34</v>
+        <v>326.29</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:36:08</t>
+          <t>09:32:22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>10.93</v>
       </c>
       <c r="G88" t="n">
-        <v>288.5</v>
+        <v>289.2</v>
       </c>
       <c r="H88" t="n">
-        <v>38.3</v>
+        <v>43.5</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.02</v>
+        <v>144.51</v>
       </c>
       <c r="K88" t="n">
-        <v>-319.48</v>
+        <v>-159.57</v>
       </c>
       <c r="L88" t="n">
-        <v>319.52</v>
+        <v>215.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-17.xlsx
+++ b/output/2025-08-17.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-29.61</v>
+        <v>-27.35</v>
       </c>
       <c r="K14" t="n">
-        <v>110.57</v>
+        <v>102.16</v>
       </c>
       <c r="L14" t="n">
-        <v>114.47</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>10.11</v>
+        <v>11.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-72.91</v>
+        <v>-84.08</v>
       </c>
       <c r="L15" t="n">
-        <v>73.61</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-127.77</v>
+        <v>-131.64</v>
       </c>
       <c r="K16" t="n">
-        <v>168.16</v>
+        <v>173.26</v>
       </c>
       <c r="L16" t="n">
-        <v>211.2</v>
+        <v>217.6</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>111.36</v>
+        <v>121.46</v>
       </c>
       <c r="K17" t="n">
-        <v>30.8</v>
+        <v>33.6</v>
       </c>
       <c r="L17" t="n">
-        <v>115.54</v>
+        <v>126.02</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>39.68</v>
+        <v>38.2</v>
       </c>
       <c r="K18" t="n">
-        <v>158.51</v>
+        <v>152.59</v>
       </c>
       <c r="L18" t="n">
-        <v>163.4</v>
+        <v>157.3</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-51.8</v>
+        <v>-69.98999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-67.84</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>85.34999999999999</v>
+        <v>115.32</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>427.24</v>
+        <v>400.36</v>
       </c>
       <c r="K20" t="n">
-        <v>-144.46</v>
+        <v>-135.37</v>
       </c>
       <c r="L20" t="n">
-        <v>451</v>
+        <v>422.62</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.6</v>
+        <v>-30.73</v>
       </c>
       <c r="K21" t="n">
-        <v>-278.27</v>
+        <v>-279.51</v>
       </c>
       <c r="L21" t="n">
-        <v>279.95</v>
+        <v>281.2</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>12.06</v>
+        <v>18.21</v>
       </c>
       <c r="K22" t="n">
-        <v>111.55</v>
+        <v>168.45</v>
       </c>
       <c r="L22" t="n">
-        <v>112.19</v>
+        <v>169.43</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-19.3</v>
+        <v>-24.69</v>
       </c>
       <c r="K23" t="n">
-        <v>-336.93</v>
+        <v>-431.06</v>
       </c>
       <c r="L23" t="n">
-        <v>337.48</v>
+        <v>431.77</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-366.07</v>
+        <v>-442.2</v>
       </c>
       <c r="K24" t="n">
-        <v>181.08</v>
+        <v>218.74</v>
       </c>
       <c r="L24" t="n">
-        <v>408.41</v>
+        <v>493.35</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.28</v>
+        <v>-0.37</v>
       </c>
       <c r="K25" t="n">
-        <v>298.95</v>
+        <v>397.07</v>
       </c>
       <c r="L25" t="n">
-        <v>298.95</v>
+        <v>397.07</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>42.55</v>
+        <v>62.86</v>
       </c>
       <c r="K26" t="n">
-        <v>372.15</v>
+        <v>549.8099999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>374.57</v>
+        <v>553.4</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>783.0700000000001</v>
+        <v>801.33</v>
       </c>
       <c r="K27" t="n">
-        <v>417.73</v>
+        <v>427.47</v>
       </c>
       <c r="L27" t="n">
-        <v>887.52</v>
+        <v>908.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>114.07</v>
+        <v>150.65</v>
       </c>
       <c r="K28" t="n">
-        <v>400.75</v>
+        <v>529.26</v>
       </c>
       <c r="L28" t="n">
-        <v>416.67</v>
+        <v>550.28</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.84</v>
+        <v>-20.87</v>
       </c>
       <c r="K29" t="n">
-        <v>-107.06</v>
+        <v>-93.75</v>
       </c>
       <c r="L29" t="n">
-        <v>109.68</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-54.15</v>
+        <v>-49.82</v>
       </c>
       <c r="K30" t="n">
-        <v>174.89</v>
+        <v>160.89</v>
       </c>
       <c r="L30" t="n">
-        <v>183.08</v>
+        <v>168.43</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-79.7</v>
+        <v>-87.03</v>
       </c>
       <c r="K31" t="n">
-        <v>-118.8</v>
+        <v>-129.73</v>
       </c>
       <c r="L31" t="n">
-        <v>143.05</v>
+        <v>156.22</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>34.25</v>
+        <v>37.14</v>
       </c>
       <c r="K32" t="n">
-        <v>207.64</v>
+        <v>225.15</v>
       </c>
       <c r="L32" t="n">
-        <v>210.45</v>
+        <v>228.19</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>76.59</v>
+        <v>99.05</v>
       </c>
       <c r="K33" t="n">
-        <v>-32.34</v>
+        <v>-41.82</v>
       </c>
       <c r="L33" t="n">
-        <v>83.14</v>
+        <v>107.51</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-55.27</v>
+        <v>-92.15000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>23.97</v>
+        <v>39.96</v>
       </c>
       <c r="L34" t="n">
-        <v>60.25</v>
+        <v>100.44</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>117.46</v>
+        <v>152.37</v>
       </c>
       <c r="K35" t="n">
-        <v>138.05</v>
+        <v>179.08</v>
       </c>
       <c r="L35" t="n">
-        <v>181.26</v>
+        <v>235.12</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>233.01</v>
+        <v>330.46</v>
       </c>
       <c r="K36" t="n">
-        <v>-107.93</v>
+        <v>-153.07</v>
       </c>
       <c r="L36" t="n">
-        <v>256.8</v>
+        <v>364.19</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-47.79</v>
+        <v>-148.74</v>
       </c>
       <c r="K37" t="n">
-        <v>27.27</v>
+        <v>84.88</v>
       </c>
       <c r="L37" t="n">
-        <v>55.03</v>
+        <v>171.26</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-365.93</v>
+        <v>-389.99</v>
       </c>
       <c r="K38" t="n">
-        <v>177.41</v>
+        <v>189.07</v>
       </c>
       <c r="L38" t="n">
-        <v>406.67</v>
+        <v>433.4</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-554.39</v>
+        <v>-482.68</v>
       </c>
       <c r="K39" t="n">
-        <v>-142.81</v>
+        <v>-124.34</v>
       </c>
       <c r="L39" t="n">
-        <v>572.49</v>
+        <v>498.44</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>96.59999999999999</v>
+        <v>152.2</v>
       </c>
       <c r="K40" t="n">
-        <v>156.33</v>
+        <v>246.32</v>
       </c>
       <c r="L40" t="n">
-        <v>183.77</v>
+        <v>289.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-452.5</v>
+        <v>-526.15</v>
       </c>
       <c r="K41" t="n">
-        <v>672.8099999999999</v>
+        <v>782.3200000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>810.8200000000001</v>
+        <v>942.79</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-675.7</v>
+        <v>-911.25</v>
       </c>
       <c r="K42" t="n">
-        <v>54.67</v>
+        <v>73.73</v>
       </c>
       <c r="L42" t="n">
-        <v>677.91</v>
+        <v>914.23</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>228.73</v>
+        <v>416.74</v>
       </c>
       <c r="K43" t="n">
-        <v>149.28</v>
+        <v>271.98</v>
       </c>
       <c r="L43" t="n">
-        <v>273.13</v>
+        <v>497.64</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-58.2</v>
+        <v>-72.38</v>
       </c>
       <c r="K44" t="n">
-        <v>174.2</v>
+        <v>216.66</v>
       </c>
       <c r="L44" t="n">
-        <v>183.66</v>
+        <v>228.43</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.26</v>
+        <v>-5.89</v>
       </c>
       <c r="K45" t="n">
-        <v>114.03</v>
+        <v>157.81</v>
       </c>
       <c r="L45" t="n">
-        <v>114.11</v>
+        <v>157.92</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>107.88</v>
+        <v>111.4</v>
       </c>
       <c r="K46" t="n">
-        <v>-205.49</v>
+        <v>-212.19</v>
       </c>
       <c r="L46" t="n">
-        <v>232.09</v>
+        <v>239.66</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>83.2</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>196.48</v>
+        <v>178.8</v>
       </c>
       <c r="L47" t="n">
-        <v>213.37</v>
+        <v>194.16</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>46.45</v>
+        <v>73.13</v>
       </c>
       <c r="K48" t="n">
-        <v>50.8</v>
+        <v>79.98</v>
       </c>
       <c r="L48" t="n">
-        <v>68.84</v>
+        <v>108.37</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-271.38</v>
+        <v>-279.66</v>
       </c>
       <c r="K49" t="n">
-        <v>-305.07</v>
+        <v>-314.37</v>
       </c>
       <c r="L49" t="n">
-        <v>408.31</v>
+        <v>420.76</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-102.22</v>
+        <v>-91.48999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>347.14</v>
+        <v>310.72</v>
       </c>
       <c r="L50" t="n">
-        <v>361.87</v>
+        <v>323.91</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-339.65</v>
+        <v>-341.6</v>
       </c>
       <c r="K51" t="n">
-        <v>-116.74</v>
+        <v>-117.41</v>
       </c>
       <c r="L51" t="n">
-        <v>359.15</v>
+        <v>361.21</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-236.22</v>
+        <v>-261.13</v>
       </c>
       <c r="K52" t="n">
-        <v>-29.54</v>
+        <v>-32.66</v>
       </c>
       <c r="L52" t="n">
-        <v>238.06</v>
+        <v>263.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>426.31</v>
+        <v>460.91</v>
       </c>
       <c r="K53" t="n">
-        <v>-30.43</v>
+        <v>-32.9</v>
       </c>
       <c r="L53" t="n">
-        <v>427.4</v>
+        <v>462.08</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-242.56</v>
+        <v>-275.55</v>
       </c>
       <c r="K54" t="n">
-        <v>293.17</v>
+        <v>333.05</v>
       </c>
       <c r="L54" t="n">
-        <v>380.5</v>
+        <v>432.26</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>86.72</v>
+        <v>128.56</v>
       </c>
       <c r="K55" t="n">
-        <v>-242.5</v>
+        <v>-359.52</v>
       </c>
       <c r="L55" t="n">
-        <v>257.54</v>
+        <v>381.81</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>24.4</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>85.05</v>
+        <v>279.44</v>
       </c>
       <c r="L56" t="n">
-        <v>88.48</v>
+        <v>290.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>207.86</v>
+        <v>301.91</v>
       </c>
       <c r="K57" t="n">
-        <v>-398.21</v>
+        <v>-578.4</v>
       </c>
       <c r="L57" t="n">
-        <v>449.2</v>
+        <v>652.45</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>242.4</v>
+        <v>346.89</v>
       </c>
       <c r="K58" t="n">
-        <v>-175.02</v>
+        <v>-250.46</v>
       </c>
       <c r="L58" t="n">
-        <v>298.98</v>
+        <v>427.85</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>6.85</v>
+        <v>9.23</v>
       </c>
       <c r="K59" t="n">
-        <v>-111.5</v>
+        <v>-150.15</v>
       </c>
       <c r="L59" t="n">
-        <v>111.71</v>
+        <v>150.44</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.98</v>
+        <v>-21.23</v>
       </c>
       <c r="K60" t="n">
-        <v>-179.36</v>
+        <v>-173.27</v>
       </c>
       <c r="L60" t="n">
-        <v>180.7</v>
+        <v>174.56</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>51.32</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>75.72</v>
+        <v>98.72</v>
       </c>
       <c r="L61" t="n">
-        <v>91.47</v>
+        <v>119.25</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-167.53</v>
+        <v>-183.71</v>
       </c>
       <c r="K62" t="n">
-        <v>89.08</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>189.74</v>
+        <v>208.07</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-114.14</v>
+        <v>-130.08</v>
       </c>
       <c r="K63" t="n">
-        <v>83.79000000000001</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>141.6</v>
+        <v>161.37</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-117.16</v>
+        <v>-135.44</v>
       </c>
       <c r="K64" t="n">
-        <v>117.83</v>
+        <v>136.22</v>
       </c>
       <c r="L64" t="n">
-        <v>166.17</v>
+        <v>192.09</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>196.15</v>
+        <v>244.01</v>
       </c>
       <c r="K65" t="n">
-        <v>97.86</v>
+        <v>121.73</v>
       </c>
       <c r="L65" t="n">
-        <v>219.21</v>
+        <v>272.69</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>417.54</v>
+        <v>385.81</v>
       </c>
       <c r="K66" t="n">
-        <v>105.43</v>
+        <v>97.42</v>
       </c>
       <c r="L66" t="n">
-        <v>430.65</v>
+        <v>397.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-95.39</v>
+        <v>-110.42</v>
       </c>
       <c r="K67" t="n">
-        <v>310.26</v>
+        <v>359.14</v>
       </c>
       <c r="L67" t="n">
-        <v>324.59</v>
+        <v>375.73</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-242.97</v>
+        <v>-320.46</v>
       </c>
       <c r="K68" t="n">
-        <v>-163.24</v>
+        <v>-215.31</v>
       </c>
       <c r="L68" t="n">
-        <v>292.71</v>
+        <v>386.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>113.94</v>
+        <v>187.84</v>
       </c>
       <c r="K69" t="n">
-        <v>-121.93</v>
+        <v>-201.01</v>
       </c>
       <c r="L69" t="n">
-        <v>166.87</v>
+        <v>275.12</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-84.29000000000001</v>
+        <v>-92.98</v>
       </c>
       <c r="K70" t="n">
-        <v>-376.49</v>
+        <v>-415.3</v>
       </c>
       <c r="L70" t="n">
-        <v>385.81</v>
+        <v>425.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-255.37</v>
+        <v>-316.57</v>
       </c>
       <c r="K71" t="n">
-        <v>-299.65</v>
+        <v>-371.45</v>
       </c>
       <c r="L71" t="n">
-        <v>393.7</v>
+        <v>488.05</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>121.62</v>
+        <v>287.53</v>
       </c>
       <c r="K72" t="n">
-        <v>-134.34</v>
+        <v>-317.61</v>
       </c>
       <c r="L72" t="n">
-        <v>181.21</v>
+        <v>428.43</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>153.99</v>
+        <v>264.96</v>
       </c>
       <c r="K73" t="n">
-        <v>-31.7</v>
+        <v>-54.55</v>
       </c>
       <c r="L73" t="n">
-        <v>157.22</v>
+        <v>270.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-98.66</v>
+        <v>-115.13</v>
       </c>
       <c r="K74" t="n">
-        <v>-49.44</v>
+        <v>-57.7</v>
       </c>
       <c r="L74" t="n">
-        <v>110.35</v>
+        <v>128.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-174.04</v>
+        <v>-175.22</v>
       </c>
       <c r="K75" t="n">
-        <v>20.85</v>
+        <v>20.99</v>
       </c>
       <c r="L75" t="n">
-        <v>175.28</v>
+        <v>176.48</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>143.3</v>
+        <v>177.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.64</v>
+        <v>-41.56</v>
       </c>
       <c r="L76" t="n">
-        <v>147.2</v>
+        <v>181.87</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-82.25</v>
+        <v>-81.17</v>
       </c>
       <c r="K77" t="n">
-        <v>-173.57</v>
+        <v>-171.3</v>
       </c>
       <c r="L77" t="n">
-        <v>192.07</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>151.05</v>
+        <v>149.51</v>
       </c>
       <c r="K78" t="n">
-        <v>347.6</v>
+        <v>344.07</v>
       </c>
       <c r="L78" t="n">
-        <v>379</v>
+        <v>375.15</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-115.56</v>
+        <v>-125.09</v>
       </c>
       <c r="K79" t="n">
-        <v>145.75</v>
+        <v>157.78</v>
       </c>
       <c r="L79" t="n">
-        <v>186</v>
+        <v>201.35</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>103.52</v>
+        <v>133.68</v>
       </c>
       <c r="K80" t="n">
-        <v>-157.83</v>
+        <v>-203.82</v>
       </c>
       <c r="L80" t="n">
-        <v>188.75</v>
+        <v>243.75</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-111.15</v>
+        <v>-168.24</v>
       </c>
       <c r="K81" t="n">
-        <v>-165.33</v>
+        <v>-250.24</v>
       </c>
       <c r="L81" t="n">
-        <v>199.22</v>
+        <v>301.53</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-320.15</v>
+        <v>-348.12</v>
       </c>
       <c r="K82" t="n">
-        <v>-12.21</v>
+        <v>-13.27</v>
       </c>
       <c r="L82" t="n">
-        <v>320.39</v>
+        <v>348.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>317.86</v>
+        <v>399.54</v>
       </c>
       <c r="K83" t="n">
-        <v>139.29</v>
+        <v>175.08</v>
       </c>
       <c r="L83" t="n">
-        <v>347.04</v>
+        <v>436.21</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>192.3</v>
+        <v>234.13</v>
       </c>
       <c r="K84" t="n">
-        <v>343.9</v>
+        <v>418.71</v>
       </c>
       <c r="L84" t="n">
-        <v>394.01</v>
+        <v>479.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-212.85</v>
+        <v>-408.13</v>
       </c>
       <c r="K85" t="n">
-        <v>-58.21</v>
+        <v>-111.6</v>
       </c>
       <c r="L85" t="n">
-        <v>220.67</v>
+        <v>423.11</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>490.94</v>
+        <v>644.49</v>
       </c>
       <c r="K86" t="n">
-        <v>256.26</v>
+        <v>336.4</v>
       </c>
       <c r="L86" t="n">
-        <v>553.8</v>
+        <v>727</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>9.359999999999999</v>
+        <v>14.04</v>
       </c>
       <c r="K87" t="n">
-        <v>-326.16</v>
+        <v>-489.27</v>
       </c>
       <c r="L87" t="n">
-        <v>326.29</v>
+        <v>489.47</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>144.51</v>
+        <v>270.01</v>
       </c>
       <c r="K88" t="n">
-        <v>-159.57</v>
+        <v>-298.15</v>
       </c>
       <c r="L88" t="n">
-        <v>215.28</v>
+        <v>402.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-17.xlsx
+++ b/output/2025-08-17.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-27.35</v>
+        <v>-22.74</v>
       </c>
       <c r="K14" t="n">
-        <v>102.16</v>
+        <v>84.92</v>
       </c>
       <c r="L14" t="n">
-        <v>105.76</v>
+        <v>87.92</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>11.66</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-84.08</v>
+        <v>-72.13</v>
       </c>
       <c r="L15" t="n">
-        <v>84.88</v>
+        <v>72.81999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-131.64</v>
+        <v>-100.44</v>
       </c>
       <c r="K16" t="n">
-        <v>173.26</v>
+        <v>132.2</v>
       </c>
       <c r="L16" t="n">
-        <v>217.6</v>
+        <v>166.02</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>121.46</v>
+        <v>95.33</v>
       </c>
       <c r="K17" t="n">
-        <v>33.6</v>
+        <v>26.37</v>
       </c>
       <c r="L17" t="n">
-        <v>126.02</v>
+        <v>98.91</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>38.2</v>
+        <v>28.17</v>
       </c>
       <c r="K18" t="n">
-        <v>152.59</v>
+        <v>112.53</v>
       </c>
       <c r="L18" t="n">
-        <v>157.3</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-69.98999999999999</v>
+        <v>-51.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-91.65000000000001</v>
+        <v>-67.19</v>
       </c>
       <c r="L19" t="n">
-        <v>115.32</v>
+        <v>84.54000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>400.36</v>
+        <v>241.46</v>
       </c>
       <c r="K20" t="n">
-        <v>-135.37</v>
+        <v>-81.65000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>422.62</v>
+        <v>254.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.73</v>
+        <v>-19.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-279.51</v>
+        <v>-178.33</v>
       </c>
       <c r="L21" t="n">
-        <v>281.2</v>
+        <v>179.41</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>18.21</v>
+        <v>11.46</v>
       </c>
       <c r="K22" t="n">
-        <v>168.45</v>
+        <v>106.06</v>
       </c>
       <c r="L22" t="n">
-        <v>169.43</v>
+        <v>106.68</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-24.69</v>
+        <v>-12.72</v>
       </c>
       <c r="K23" t="n">
-        <v>-431.06</v>
+        <v>-222.04</v>
       </c>
       <c r="L23" t="n">
-        <v>431.77</v>
+        <v>222.4</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-442.2</v>
+        <v>-240.86</v>
       </c>
       <c r="K24" t="n">
-        <v>218.74</v>
+        <v>119.15</v>
       </c>
       <c r="L24" t="n">
-        <v>493.35</v>
+        <v>268.72</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.37</v>
+        <v>-0.21</v>
       </c>
       <c r="K25" t="n">
-        <v>397.07</v>
+        <v>227.39</v>
       </c>
       <c r="L25" t="n">
-        <v>397.07</v>
+        <v>227.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>62.86</v>
+        <v>31.19</v>
       </c>
       <c r="K26" t="n">
-        <v>549.8099999999999</v>
+        <v>272.78</v>
       </c>
       <c r="L26" t="n">
-        <v>553.4</v>
+        <v>274.55</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>801.33</v>
+        <v>405.71</v>
       </c>
       <c r="K27" t="n">
-        <v>427.47</v>
+        <v>216.43</v>
       </c>
       <c r="L27" t="n">
-        <v>908.22</v>
+        <v>459.83</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>150.65</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>529.26</v>
+        <v>280.9</v>
       </c>
       <c r="L28" t="n">
-        <v>550.28</v>
+        <v>292.06</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-20.87</v>
+        <v>-17.27</v>
       </c>
       <c r="K29" t="n">
-        <v>-93.75</v>
+        <v>-77.56</v>
       </c>
       <c r="L29" t="n">
-        <v>96.05</v>
+        <v>79.45999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-49.82</v>
+        <v>-39.21</v>
       </c>
       <c r="K30" t="n">
-        <v>160.89</v>
+        <v>126.63</v>
       </c>
       <c r="L30" t="n">
-        <v>168.43</v>
+        <v>132.57</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-87.03</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-129.73</v>
+        <v>-96.95</v>
       </c>
       <c r="L31" t="n">
-        <v>156.22</v>
+        <v>116.74</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>37.14</v>
+        <v>25.03</v>
       </c>
       <c r="K32" t="n">
-        <v>225.15</v>
+        <v>151.72</v>
       </c>
       <c r="L32" t="n">
-        <v>228.19</v>
+        <v>153.77</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>99.05</v>
+        <v>79.52</v>
       </c>
       <c r="K33" t="n">
-        <v>-41.82</v>
+        <v>-33.58</v>
       </c>
       <c r="L33" t="n">
-        <v>107.51</v>
+        <v>86.31999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-92.15000000000001</v>
+        <v>-69.03</v>
       </c>
       <c r="K34" t="n">
-        <v>39.96</v>
+        <v>29.93</v>
       </c>
       <c r="L34" t="n">
-        <v>100.44</v>
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>152.37</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>179.08</v>
+        <v>108.5</v>
       </c>
       <c r="L35" t="n">
-        <v>235.12</v>
+        <v>142.46</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>330.46</v>
+        <v>182.68</v>
       </c>
       <c r="K36" t="n">
-        <v>-153.07</v>
+        <v>-84.62</v>
       </c>
       <c r="L36" t="n">
-        <v>364.19</v>
+        <v>201.33</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-148.74</v>
+        <v>-84.37</v>
       </c>
       <c r="K37" t="n">
-        <v>84.88</v>
+        <v>48.14</v>
       </c>
       <c r="L37" t="n">
-        <v>171.26</v>
+        <v>97.14</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-389.99</v>
+        <v>-238.2</v>
       </c>
       <c r="K38" t="n">
-        <v>189.07</v>
+        <v>115.48</v>
       </c>
       <c r="L38" t="n">
-        <v>433.4</v>
+        <v>264.72</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-482.68</v>
+        <v>-308.61</v>
       </c>
       <c r="K39" t="n">
-        <v>-124.34</v>
+        <v>-79.5</v>
       </c>
       <c r="L39" t="n">
-        <v>498.44</v>
+        <v>318.69</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>152.2</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>246.32</v>
+        <v>143.29</v>
       </c>
       <c r="L40" t="n">
-        <v>289.55</v>
+        <v>168.43</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-526.15</v>
+        <v>-255.39</v>
       </c>
       <c r="K41" t="n">
-        <v>782.3200000000001</v>
+        <v>379.73</v>
       </c>
       <c r="L41" t="n">
-        <v>942.79</v>
+        <v>457.63</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-911.25</v>
+        <v>-428.19</v>
       </c>
       <c r="K42" t="n">
-        <v>73.73</v>
+        <v>34.64</v>
       </c>
       <c r="L42" t="n">
-        <v>914.23</v>
+        <v>429.59</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>416.74</v>
+        <v>195.55</v>
       </c>
       <c r="K43" t="n">
-        <v>271.98</v>
+        <v>127.62</v>
       </c>
       <c r="L43" t="n">
-        <v>497.64</v>
+        <v>233.51</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-72.38</v>
+        <v>-48.58</v>
       </c>
       <c r="K44" t="n">
-        <v>216.66</v>
+        <v>145.4</v>
       </c>
       <c r="L44" t="n">
-        <v>228.43</v>
+        <v>153.3</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.89</v>
+        <v>-3.98</v>
       </c>
       <c r="K45" t="n">
-        <v>157.81</v>
+        <v>106.54</v>
       </c>
       <c r="L45" t="n">
-        <v>157.92</v>
+        <v>106.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>111.4</v>
+        <v>75.89</v>
       </c>
       <c r="K46" t="n">
-        <v>-212.19</v>
+        <v>-144.55</v>
       </c>
       <c r="L46" t="n">
-        <v>239.66</v>
+        <v>163.26</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>75.70999999999999</v>
+        <v>58.89</v>
       </c>
       <c r="K47" t="n">
-        <v>178.8</v>
+        <v>139.09</v>
       </c>
       <c r="L47" t="n">
-        <v>194.16</v>
+        <v>151.04</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>73.13</v>
+        <v>54.46</v>
       </c>
       <c r="K48" t="n">
-        <v>79.98</v>
+        <v>59.56</v>
       </c>
       <c r="L48" t="n">
-        <v>108.37</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-279.66</v>
+        <v>-183.81</v>
       </c>
       <c r="K49" t="n">
-        <v>-314.37</v>
+        <v>-206.63</v>
       </c>
       <c r="L49" t="n">
-        <v>420.76</v>
+        <v>276.56</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-91.48999999999999</v>
+        <v>-64.7</v>
       </c>
       <c r="K50" t="n">
-        <v>310.72</v>
+        <v>219.73</v>
       </c>
       <c r="L50" t="n">
-        <v>323.91</v>
+        <v>229.06</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-341.6</v>
+        <v>-231.35</v>
       </c>
       <c r="K51" t="n">
-        <v>-117.41</v>
+        <v>-79.52</v>
       </c>
       <c r="L51" t="n">
-        <v>361.21</v>
+        <v>244.63</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-261.13</v>
+        <v>-174.78</v>
       </c>
       <c r="K52" t="n">
-        <v>-32.66</v>
+        <v>-21.86</v>
       </c>
       <c r="L52" t="n">
-        <v>263.16</v>
+        <v>176.14</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>460.91</v>
+        <v>278.7</v>
       </c>
       <c r="K53" t="n">
-        <v>-32.9</v>
+        <v>-19.9</v>
       </c>
       <c r="L53" t="n">
-        <v>462.08</v>
+        <v>279.41</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-275.55</v>
+        <v>-151.77</v>
       </c>
       <c r="K54" t="n">
-        <v>333.05</v>
+        <v>183.44</v>
       </c>
       <c r="L54" t="n">
-        <v>432.26</v>
+        <v>238.08</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>128.56</v>
+        <v>72.88</v>
       </c>
       <c r="K55" t="n">
-        <v>-359.52</v>
+        <v>-203.8</v>
       </c>
       <c r="L55" t="n">
-        <v>381.81</v>
+        <v>216.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>80.18000000000001</v>
+        <v>43.51</v>
       </c>
       <c r="K56" t="n">
-        <v>279.44</v>
+        <v>151.63</v>
       </c>
       <c r="L56" t="n">
-        <v>290.72</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>301.91</v>
+        <v>144.76</v>
       </c>
       <c r="K57" t="n">
-        <v>-578.4</v>
+        <v>-277.33</v>
       </c>
       <c r="L57" t="n">
-        <v>652.45</v>
+        <v>312.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>346.89</v>
+        <v>192.53</v>
       </c>
       <c r="K58" t="n">
-        <v>-250.46</v>
+        <v>-139.01</v>
       </c>
       <c r="L58" t="n">
-        <v>427.85</v>
+        <v>237.47</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>9.23</v>
+        <v>6.68</v>
       </c>
       <c r="K59" t="n">
-        <v>-150.15</v>
+        <v>-108.69</v>
       </c>
       <c r="L59" t="n">
-        <v>150.44</v>
+        <v>108.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-21.23</v>
+        <v>-16.82</v>
       </c>
       <c r="K60" t="n">
-        <v>-173.27</v>
+        <v>-137.25</v>
       </c>
       <c r="L60" t="n">
-        <v>174.56</v>
+        <v>138.27</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>66.90000000000001</v>
+        <v>48.21</v>
       </c>
       <c r="K61" t="n">
-        <v>98.72</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>119.25</v>
+        <v>85.95</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-183.71</v>
+        <v>-122.53</v>
       </c>
       <c r="K62" t="n">
-        <v>97.68000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>208.07</v>
+        <v>138.77</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-130.08</v>
+        <v>-95.59999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>95.48999999999999</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>161.37</v>
+        <v>118.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-135.44</v>
+        <v>-91.78</v>
       </c>
       <c r="K64" t="n">
-        <v>136.22</v>
+        <v>92.31</v>
       </c>
       <c r="L64" t="n">
-        <v>192.09</v>
+        <v>130.17</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>244.01</v>
+        <v>162.78</v>
       </c>
       <c r="K65" t="n">
-        <v>121.73</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>272.69</v>
+        <v>181.91</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>385.81</v>
+        <v>264.92</v>
       </c>
       <c r="K66" t="n">
-        <v>97.42</v>
+        <v>66.89</v>
       </c>
       <c r="L66" t="n">
-        <v>397.92</v>
+        <v>273.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-110.42</v>
+        <v>-63.41</v>
       </c>
       <c r="K67" t="n">
-        <v>359.14</v>
+        <v>206.24</v>
       </c>
       <c r="L67" t="n">
-        <v>375.73</v>
+        <v>215.77</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-320.46</v>
+        <v>-189.58</v>
       </c>
       <c r="K68" t="n">
-        <v>-215.31</v>
+        <v>-127.37</v>
       </c>
       <c r="L68" t="n">
-        <v>386.08</v>
+        <v>228.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>187.84</v>
+        <v>106.67</v>
       </c>
       <c r="K69" t="n">
-        <v>-201.01</v>
+        <v>-114.15</v>
       </c>
       <c r="L69" t="n">
-        <v>275.12</v>
+        <v>156.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-92.98</v>
+        <v>-56.41</v>
       </c>
       <c r="K70" t="n">
-        <v>-415.3</v>
+        <v>-251.94</v>
       </c>
       <c r="L70" t="n">
-        <v>425.58</v>
+        <v>258.18</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-316.57</v>
+        <v>-172.98</v>
       </c>
       <c r="K71" t="n">
-        <v>-371.45</v>
+        <v>-202.97</v>
       </c>
       <c r="L71" t="n">
-        <v>488.05</v>
+        <v>266.68</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>287.53</v>
+        <v>133.74</v>
       </c>
       <c r="K72" t="n">
-        <v>-317.61</v>
+        <v>-147.74</v>
       </c>
       <c r="L72" t="n">
-        <v>428.43</v>
+        <v>199.28</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>264.96</v>
+        <v>153.07</v>
       </c>
       <c r="K73" t="n">
-        <v>-54.55</v>
+        <v>-31.51</v>
       </c>
       <c r="L73" t="n">
-        <v>270.52</v>
+        <v>156.28</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-115.13</v>
+        <v>-88.68000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-57.7</v>
+        <v>-44.44</v>
       </c>
       <c r="L74" t="n">
-        <v>128.78</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-175.22</v>
+        <v>-128.52</v>
       </c>
       <c r="K75" t="n">
-        <v>20.99</v>
+        <v>15.4</v>
       </c>
       <c r="L75" t="n">
-        <v>176.48</v>
+        <v>129.44</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>177.06</v>
+        <v>121.61</v>
       </c>
       <c r="K76" t="n">
-        <v>-41.56</v>
+        <v>-28.55</v>
       </c>
       <c r="L76" t="n">
-        <v>181.87</v>
+        <v>124.92</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-81.17</v>
+        <v>-61.93</v>
       </c>
       <c r="K77" t="n">
-        <v>-171.3</v>
+        <v>-130.68</v>
       </c>
       <c r="L77" t="n">
-        <v>189.56</v>
+        <v>144.61</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>149.51</v>
+        <v>96.48</v>
       </c>
       <c r="K78" t="n">
-        <v>344.07</v>
+        <v>222.03</v>
       </c>
       <c r="L78" t="n">
-        <v>375.15</v>
+        <v>242.09</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-125.09</v>
+        <v>-90.73</v>
       </c>
       <c r="K79" t="n">
-        <v>157.78</v>
+        <v>114.44</v>
       </c>
       <c r="L79" t="n">
-        <v>201.35</v>
+        <v>146.05</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>133.68</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-203.82</v>
+        <v>-136.62</v>
       </c>
       <c r="L80" t="n">
-        <v>243.75</v>
+        <v>163.38</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-168.24</v>
+        <v>-95.61</v>
       </c>
       <c r="K81" t="n">
-        <v>-250.24</v>
+        <v>-142.22</v>
       </c>
       <c r="L81" t="n">
-        <v>301.53</v>
+        <v>171.37</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-348.12</v>
+        <v>-231.9</v>
       </c>
       <c r="K82" t="n">
-        <v>-13.27</v>
+        <v>-8.84</v>
       </c>
       <c r="L82" t="n">
-        <v>348.37</v>
+        <v>232.07</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>399.54</v>
+        <v>214.17</v>
       </c>
       <c r="K83" t="n">
-        <v>175.08</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>436.21</v>
+        <v>233.84</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>234.13</v>
+        <v>127.69</v>
       </c>
       <c r="K84" t="n">
-        <v>418.71</v>
+        <v>228.35</v>
       </c>
       <c r="L84" t="n">
-        <v>479.72</v>
+        <v>261.63</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-408.13</v>
+        <v>-197.23</v>
       </c>
       <c r="K85" t="n">
-        <v>-111.6</v>
+        <v>-53.93</v>
       </c>
       <c r="L85" t="n">
-        <v>423.11</v>
+        <v>204.47</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>644.49</v>
+        <v>310.96</v>
       </c>
       <c r="K86" t="n">
-        <v>336.4</v>
+        <v>162.31</v>
       </c>
       <c r="L86" t="n">
-        <v>727</v>
+        <v>350.78</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>14.04</v>
+        <v>7.39</v>
       </c>
       <c r="K87" t="n">
-        <v>-489.27</v>
+        <v>-257.54</v>
       </c>
       <c r="L87" t="n">
-        <v>489.47</v>
+        <v>257.64</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>270.01</v>
+        <v>138.06</v>
       </c>
       <c r="K88" t="n">
-        <v>-298.15</v>
+        <v>-152.45</v>
       </c>
       <c r="L88" t="n">
-        <v>402.24</v>
+        <v>205.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-17.xlsx
+++ b/output/2025-08-17.xlsx
@@ -640,13 +640,13 @@
         <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-22.74</v>
+        <v>-22.32</v>
       </c>
       <c r="K14" t="n">
-        <v>84.92</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>87.92</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-72.13</v>
+        <v>-69.51000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>72.81999999999999</v>
+        <v>70.18000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-100.44</v>
+        <v>-100.56</v>
       </c>
       <c r="K16" t="n">
-        <v>132.2</v>
+        <v>132.35</v>
       </c>
       <c r="L16" t="n">
-        <v>166.02</v>
+        <v>166.22</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>95.33</v>
+        <v>97.45</v>
       </c>
       <c r="K17" t="n">
-        <v>26.37</v>
+        <v>26.95</v>
       </c>
       <c r="L17" t="n">
-        <v>98.91</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>28.17</v>
+        <v>28.77</v>
       </c>
       <c r="K18" t="n">
-        <v>112.53</v>
+        <v>114.91</v>
       </c>
       <c r="L18" t="n">
-        <v>116</v>
+        <v>118.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-51.3</v>
+        <v>-52.8</v>
       </c>
       <c r="K19" t="n">
-        <v>-67.19</v>
+        <v>-69.15000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>84.54000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>241.46</v>
+        <v>263.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-81.65000000000001</v>
+        <v>-89.26000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>254.89</v>
+        <v>278.67</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.61</v>
+        <v>-21.08</v>
       </c>
       <c r="K21" t="n">
-        <v>-178.33</v>
+        <v>-191.73</v>
       </c>
       <c r="L21" t="n">
-        <v>179.41</v>
+        <v>192.88</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>21</v>
       </c>
       <c r="J22" t="n">
-        <v>11.46</v>
+        <v>12.22</v>
       </c>
       <c r="K22" t="n">
-        <v>106.06</v>
+        <v>113.02</v>
       </c>
       <c r="L22" t="n">
-        <v>106.68</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-12.72</v>
+        <v>-14.1</v>
       </c>
       <c r="K23" t="n">
-        <v>-222.04</v>
+        <v>-246.24</v>
       </c>
       <c r="L23" t="n">
-        <v>222.4</v>
+        <v>246.64</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-240.86</v>
+        <v>-261.2</v>
       </c>
       <c r="K24" t="n">
-        <v>119.15</v>
+        <v>129.21</v>
       </c>
       <c r="L24" t="n">
-        <v>268.72</v>
+        <v>291.41</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="K25" t="n">
-        <v>227.39</v>
+        <v>243.71</v>
       </c>
       <c r="L25" t="n">
-        <v>227.39</v>
+        <v>243.71</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>22</v>
       </c>
       <c r="J26" t="n">
-        <v>31.19</v>
+        <v>34.47</v>
       </c>
       <c r="K26" t="n">
-        <v>272.78</v>
+        <v>301.52</v>
       </c>
       <c r="L26" t="n">
-        <v>274.55</v>
+        <v>303.49</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>405.71</v>
+        <v>451.74</v>
       </c>
       <c r="K27" t="n">
-        <v>216.43</v>
+        <v>240.98</v>
       </c>
       <c r="L27" t="n">
-        <v>459.83</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>79.95999999999999</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>280.9</v>
+        <v>305.79</v>
       </c>
       <c r="L28" t="n">
-        <v>292.06</v>
+        <v>317.94</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-17.27</v>
+        <v>-17.25</v>
       </c>
       <c r="K29" t="n">
-        <v>-77.56</v>
+        <v>-77.47</v>
       </c>
       <c r="L29" t="n">
-        <v>79.45999999999999</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-39.21</v>
+        <v>-38.61</v>
       </c>
       <c r="K30" t="n">
-        <v>126.63</v>
+        <v>124.71</v>
       </c>
       <c r="L30" t="n">
-        <v>132.57</v>
+        <v>130.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-65.04000000000001</v>
+        <v>-64.41</v>
       </c>
       <c r="K31" t="n">
-        <v>-96.95</v>
+        <v>-96.01000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>116.74</v>
+        <v>115.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>25.03</v>
+        <v>26.38</v>
       </c>
       <c r="K32" t="n">
-        <v>151.72</v>
+        <v>159.96</v>
       </c>
       <c r="L32" t="n">
-        <v>153.77</v>
+        <v>162.12</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>79.52</v>
+        <v>81.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-33.58</v>
+        <v>-34.3</v>
       </c>
       <c r="L33" t="n">
-        <v>86.31999999999999</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-69.03</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>29.93</v>
+        <v>30.77</v>
       </c>
       <c r="L34" t="n">
-        <v>75.23999999999999</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>92.31999999999999</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>108.5</v>
+        <v>116.18</v>
       </c>
       <c r="L35" t="n">
-        <v>142.46</v>
+        <v>152.54</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>182.68</v>
+        <v>197.65</v>
       </c>
       <c r="K36" t="n">
-        <v>-84.62</v>
+        <v>-91.56</v>
       </c>
       <c r="L36" t="n">
-        <v>201.33</v>
+        <v>217.83</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>-84.37</v>
+        <v>-91.63</v>
       </c>
       <c r="K37" t="n">
-        <v>48.14</v>
+        <v>52.29</v>
       </c>
       <c r="L37" t="n">
-        <v>97.14</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-238.2</v>
+        <v>-255.57</v>
       </c>
       <c r="K38" t="n">
-        <v>115.48</v>
+        <v>123.9</v>
       </c>
       <c r="L38" t="n">
-        <v>264.72</v>
+        <v>284.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-308.61</v>
+        <v>-333.88</v>
       </c>
       <c r="K39" t="n">
-        <v>-79.5</v>
+        <v>-86.01000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>318.69</v>
+        <v>344.78</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>88.54000000000001</v>
+        <v>96.06</v>
       </c>
       <c r="K40" t="n">
-        <v>143.29</v>
+        <v>155.46</v>
       </c>
       <c r="L40" t="n">
-        <v>168.43</v>
+        <v>182.75</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-255.39</v>
+        <v>-286.52</v>
       </c>
       <c r="K41" t="n">
-        <v>379.73</v>
+        <v>426.03</v>
       </c>
       <c r="L41" t="n">
-        <v>457.63</v>
+        <v>513.42</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-428.19</v>
+        <v>-482.64</v>
       </c>
       <c r="K42" t="n">
-        <v>34.64</v>
+        <v>39.05</v>
       </c>
       <c r="L42" t="n">
-        <v>429.59</v>
+        <v>484.22</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>195.55</v>
+        <v>215.95</v>
       </c>
       <c r="K43" t="n">
-        <v>127.62</v>
+        <v>140.93</v>
       </c>
       <c r="L43" t="n">
-        <v>233.51</v>
+        <v>257.87</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.58</v>
+        <v>-49.6</v>
       </c>
       <c r="K44" t="n">
-        <v>145.4</v>
+        <v>148.46</v>
       </c>
       <c r="L44" t="n">
-        <v>153.3</v>
+        <v>156.53</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.98</v>
+        <v>-4.05</v>
       </c>
       <c r="K45" t="n">
-        <v>106.54</v>
+        <v>108.42</v>
       </c>
       <c r="L45" t="n">
-        <v>106.61</v>
+        <v>108.49</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>75.89</v>
+        <v>76.64</v>
       </c>
       <c r="K46" t="n">
-        <v>-144.55</v>
+        <v>-145.98</v>
       </c>
       <c r="L46" t="n">
-        <v>163.26</v>
+        <v>164.88</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>58.89</v>
+        <v>60.22</v>
       </c>
       <c r="K47" t="n">
-        <v>139.09</v>
+        <v>142.21</v>
       </c>
       <c r="L47" t="n">
-        <v>151.04</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>54.46</v>
+        <v>56.18</v>
       </c>
       <c r="K48" t="n">
-        <v>59.56</v>
+        <v>61.44</v>
       </c>
       <c r="L48" t="n">
-        <v>80.70999999999999</v>
+        <v>83.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-183.81</v>
+        <v>-190.95</v>
       </c>
       <c r="K49" t="n">
-        <v>-206.63</v>
+        <v>-214.65</v>
       </c>
       <c r="L49" t="n">
-        <v>276.56</v>
+        <v>287.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-64.7</v>
+        <v>-67.92</v>
       </c>
       <c r="K50" t="n">
-        <v>219.73</v>
+        <v>230.67</v>
       </c>
       <c r="L50" t="n">
-        <v>229.06</v>
+        <v>240.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-231.35</v>
+        <v>-243.04</v>
       </c>
       <c r="K51" t="n">
-        <v>-79.52</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>244.63</v>
+        <v>256.99</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-174.78</v>
+        <v>-184.06</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.86</v>
+        <v>-23.02</v>
       </c>
       <c r="L52" t="n">
-        <v>176.14</v>
+        <v>185.49</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>278.7</v>
+        <v>298.8</v>
       </c>
       <c r="K53" t="n">
-        <v>-19.9</v>
+        <v>-21.33</v>
       </c>
       <c r="L53" t="n">
-        <v>279.41</v>
+        <v>299.56</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-151.77</v>
+        <v>-167.82</v>
       </c>
       <c r="K54" t="n">
-        <v>183.44</v>
+        <v>202.84</v>
       </c>
       <c r="L54" t="n">
-        <v>238.08</v>
+        <v>263.26</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>72.88</v>
+        <v>78.97</v>
       </c>
       <c r="K55" t="n">
-        <v>-203.8</v>
+        <v>-220.84</v>
       </c>
       <c r="L55" t="n">
-        <v>216.44</v>
+        <v>234.54</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>43.51</v>
+        <v>47.87</v>
       </c>
       <c r="K56" t="n">
-        <v>151.63</v>
+        <v>166.83</v>
       </c>
       <c r="L56" t="n">
-        <v>157.75</v>
+        <v>173.56</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>144.76</v>
+        <v>158.54</v>
       </c>
       <c r="K57" t="n">
-        <v>-277.33</v>
+        <v>-303.72</v>
       </c>
       <c r="L57" t="n">
-        <v>312.83</v>
+        <v>342.61</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>192.53</v>
+        <v>210.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-139.01</v>
+        <v>-151.65</v>
       </c>
       <c r="L58" t="n">
-        <v>237.47</v>
+        <v>259.06</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>6.68</v>
+        <v>6.72</v>
       </c>
       <c r="K59" t="n">
-        <v>-108.69</v>
+        <v>-109.42</v>
       </c>
       <c r="L59" t="n">
-        <v>108.89</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>-16.82</v>
+        <v>-16.62</v>
       </c>
       <c r="K60" t="n">
-        <v>-137.25</v>
+        <v>-135.65</v>
       </c>
       <c r="L60" t="n">
-        <v>138.27</v>
+        <v>136.66</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>48.21</v>
+        <v>47.59</v>
       </c>
       <c r="K61" t="n">
-        <v>71.15000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="L61" t="n">
-        <v>85.95</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-122.53</v>
+        <v>-128.84</v>
       </c>
       <c r="K62" t="n">
-        <v>65.15000000000001</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>138.77</v>
+        <v>145.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-95.59999999999999</v>
+        <v>-98.91</v>
       </c>
       <c r="K63" t="n">
-        <v>70.18000000000001</v>
+        <v>72.61</v>
       </c>
       <c r="L63" t="n">
-        <v>118.59</v>
+        <v>122.69</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-91.78</v>
+        <v>-95.28</v>
       </c>
       <c r="K64" t="n">
-        <v>92.31</v>
+        <v>95.83</v>
       </c>
       <c r="L64" t="n">
-        <v>130.17</v>
+        <v>135.14</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>162.78</v>
+        <v>170.7</v>
       </c>
       <c r="K65" t="n">
-        <v>81.20999999999999</v>
+        <v>85.16</v>
       </c>
       <c r="L65" t="n">
-        <v>181.91</v>
+        <v>190.76</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>264.92</v>
+        <v>276.22</v>
       </c>
       <c r="K66" t="n">
-        <v>66.89</v>
+        <v>69.75</v>
       </c>
       <c r="L66" t="n">
-        <v>273.24</v>
+        <v>284.89</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>-63.41</v>
+        <v>-68.94</v>
       </c>
       <c r="K67" t="n">
-        <v>206.24</v>
+        <v>224.23</v>
       </c>
       <c r="L67" t="n">
-        <v>215.77</v>
+        <v>234.59</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>-189.58</v>
+        <v>-201.86</v>
       </c>
       <c r="K68" t="n">
-        <v>-127.37</v>
+        <v>-135.62</v>
       </c>
       <c r="L68" t="n">
-        <v>228.39</v>
+        <v>243.18</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>106.67</v>
+        <v>116.11</v>
       </c>
       <c r="K69" t="n">
-        <v>-114.15</v>
+        <v>-124.25</v>
       </c>
       <c r="L69" t="n">
-        <v>156.23</v>
+        <v>170.06</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-56.41</v>
+        <v>-61.09</v>
       </c>
       <c r="K70" t="n">
-        <v>-251.94</v>
+        <v>-272.84</v>
       </c>
       <c r="L70" t="n">
-        <v>258.18</v>
+        <v>279.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-172.98</v>
+        <v>-190.53</v>
       </c>
       <c r="K71" t="n">
-        <v>-202.97</v>
+        <v>-223.56</v>
       </c>
       <c r="L71" t="n">
-        <v>266.68</v>
+        <v>293.74</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>133.74</v>
+        <v>149.47</v>
       </c>
       <c r="K72" t="n">
-        <v>-147.74</v>
+        <v>-165.11</v>
       </c>
       <c r="L72" t="n">
-        <v>199.28</v>
+        <v>222.72</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>153.07</v>
+        <v>166.07</v>
       </c>
       <c r="K73" t="n">
-        <v>-31.51</v>
+        <v>-34.19</v>
       </c>
       <c r="L73" t="n">
-        <v>156.28</v>
+        <v>169.56</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-88.68000000000001</v>
+        <v>-88.29000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-44.44</v>
+        <v>-44.24</v>
       </c>
       <c r="L74" t="n">
-        <v>99.2</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-128.52</v>
+        <v>-128.2</v>
       </c>
       <c r="K75" t="n">
-        <v>15.4</v>
+        <v>15.36</v>
       </c>
       <c r="L75" t="n">
-        <v>129.44</v>
+        <v>129.12</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>121.61</v>
+        <v>123.26</v>
       </c>
       <c r="K76" t="n">
-        <v>-28.55</v>
+        <v>-28.93</v>
       </c>
       <c r="L76" t="n">
-        <v>124.92</v>
+        <v>126.62</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>-61.93</v>
+        <v>-63.37</v>
       </c>
       <c r="K77" t="n">
-        <v>-130.68</v>
+        <v>-133.73</v>
       </c>
       <c r="L77" t="n">
-        <v>144.61</v>
+        <v>147.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>96.48</v>
+        <v>100.39</v>
       </c>
       <c r="K78" t="n">
-        <v>222.03</v>
+        <v>231.03</v>
       </c>
       <c r="L78" t="n">
-        <v>242.09</v>
+        <v>251.89</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-90.73</v>
+        <v>-94.44</v>
       </c>
       <c r="K79" t="n">
-        <v>114.44</v>
+        <v>119.11</v>
       </c>
       <c r="L79" t="n">
-        <v>146.05</v>
+        <v>152.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>89.59999999999999</v>
+        <v>94.23</v>
       </c>
       <c r="K80" t="n">
-        <v>-136.62</v>
+        <v>-143.66</v>
       </c>
       <c r="L80" t="n">
-        <v>163.38</v>
+        <v>171.81</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-95.61</v>
+        <v>-102.86</v>
       </c>
       <c r="K81" t="n">
-        <v>-142.22</v>
+        <v>-153</v>
       </c>
       <c r="L81" t="n">
-        <v>171.37</v>
+        <v>184.36</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-231.9</v>
+        <v>-243.35</v>
       </c>
       <c r="K82" t="n">
-        <v>-8.84</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>232.07</v>
+        <v>243.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>214.17</v>
+        <v>235.82</v>
       </c>
       <c r="K83" t="n">
-        <v>93.84999999999999</v>
+        <v>103.34</v>
       </c>
       <c r="L83" t="n">
-        <v>233.84</v>
+        <v>257.47</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>127.69</v>
+        <v>138.66</v>
       </c>
       <c r="K84" t="n">
-        <v>228.35</v>
+        <v>247.96</v>
       </c>
       <c r="L84" t="n">
-        <v>261.63</v>
+        <v>284.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>-197.23</v>
+        <v>-219.92</v>
       </c>
       <c r="K85" t="n">
-        <v>-53.93</v>
+        <v>-60.14</v>
       </c>
       <c r="L85" t="n">
-        <v>204.47</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>310.96</v>
+        <v>344.26</v>
       </c>
       <c r="K86" t="n">
-        <v>162.31</v>
+        <v>179.69</v>
       </c>
       <c r="L86" t="n">
-        <v>350.78</v>
+        <v>388.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>7.39</v>
+        <v>8.16</v>
       </c>
       <c r="K87" t="n">
-        <v>-257.54</v>
+        <v>-284.44</v>
       </c>
       <c r="L87" t="n">
-        <v>257.64</v>
+        <v>284.56</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>138.06</v>
+        <v>151.13</v>
       </c>
       <c r="K88" t="n">
-        <v>-152.45</v>
+        <v>-166.88</v>
       </c>
       <c r="L88" t="n">
-        <v>205.67</v>
+        <v>225.14</v>
       </c>
     </row>
   </sheetData>
